--- a/60-delivery/FlatWire_TrialRunPlan.xlsx
+++ b/60-delivery/FlatWire_TrialRunPlan.xlsx
@@ -541,7 +541,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from the plan of record on August 25, 2026. Never edit this workbook — edit the plan and rebuild.</t>
+          <t>Generated from the plan of record on August 29, 2026. Never edit this workbook — edit the plan and rebuild.</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Where the 869 hours of development effort sit, by block of work and by discipline. Development only — testing, business analysis and contingency are separate and are not included.</t>
+          <t>Where the 890 hours of development effort sit, by block of work and by discipline. Development only — testing, business analysis and contingency are separate and are not included.</t>
         </is>
       </c>
     </row>
@@ -1208,14 +1208,14 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>13.7</v>
+        <v>16.9</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>11 %</t>
+          <t>12 %</t>
         </is>
       </c>
     </row>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>133.7</v>
+        <v>136.9</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -1370,14 +1370,14 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>50.6</v>
+        <v>53.8</v>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>38 %</t>
+          <t>39 %</t>
         </is>
       </c>
     </row>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>133.7</v>
+        <v>136.9</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>8</v>
@@ -1683,10 +1683,10 @@
       </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>13.7</v>
+        <v>16.9</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>264</v>
@@ -1859,10 +1859,10 @@
         <v>141</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>133.7</v>
+        <v>136.9</v>
       </c>
       <c r="H16" s="10" t="inlineStr"/>
     </row>
@@ -4786,12 +4786,25 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>One screen an engineer drives all three simulated lines from, so the acceptance run is a few clicks rather than typed commands with a stopwatch — which matters because the run is performed in front of the client and one of its checks is a three-second stop measured against a five-second threshold. It is an engineering tool, not an operator screen: it is absent from the dashboard inventory and the navigation, and it does not exist at all once the system is connected to a real machine. Several of its controls arrive switched off, because the behaviour behind them is deliberately not being built for the trial.</t>
+          <r>
+            <t xml:space="preserve">One tool an engineer drives all three simulated lines from, so the acceptance run is a few clicks rather than typed commands with a stopwatch — which matters because the run is performed in front of the client and one of its checks is a three-second stop measured against a five-second threshold. It is a </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>separate desktop application, installed only where it is needed</t>
+          </r>
+          <r>
+            <t>, rather than part of the operator system: it is absent from the dashboard inventory and the navigation, it is restricted to engineering and administration accounts, and it stops working entirely once a line is connected to a real machine. Building it separately also means it can be changed and released without touching the operator screens. Several of its controls arrive switched off, because the behaviour behind them is deliberately not being built for the trial.</t>
+          </r>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Simulator control console — screen Database (SQL Server)-sprint one</t>
+          <t>Simulator control console Database (SQL Server)-sprint one — standalone WinForms desktop tool</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -4805,10 +4818,10 @@
         </is>
       </c>
       <c r="G50" s="8" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="51">
@@ -5583,10 +5596,10 @@
       <c r="E71" s="9" t="inlineStr"/>
       <c r="F71" s="10" t="inlineStr"/>
       <c r="G71" s="10" t="n">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>133.7</v>
+        <v>136.9</v>
       </c>
     </row>
   </sheetData>
@@ -5730,11 +5743,11 @@
         <v>292</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>96 %</t>
+          <t>⚠ 103 %</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -5859,17 +5872,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Tue 3 Nov</t>
+          <t>Wed 4 Nov</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>~Mon 16 Nov</t>
+          <t>~Tue 17 Nov</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>869 h ÷ 19.5 h/day = 44.6 working days from 31 Aug, 46 once each block rounds. This is the staffed plan, not an option: it is what the team actually is</t>
+          <t>890 h ÷ 19.5 h/day = 45.6 working days from 31 Aug, 47 once each block rounds. This is the staffed plan, not an option: it is what the team actually is. (Tue 3 Nov / ~Mon 16 Nov on 869 h, before D-33)</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5894,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>~Fri 16 Oct</t>
+          <t>~Mon 19 Oct</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -5891,7 +5904,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>26.0 h/day → 34 working days. Buys back roughly two and a half weeks. The fourth pair of hands is worth most in Sprint 1, where the three tracks genuinely parallelise</t>
+          <t>26.0 h/day → 35 working days. Buys back roughly two and a half weeks. The fourth pair of hands is worth most in Sprint 1, where the three tracks genuinely parallelise</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5916,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>~Wed 7 Oct</t>
+          <t>~Thu 8 Oct</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -5913,7 +5926,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>32.5 h/day → 27 working days. Beyond Sprint 1 the chain is sequential, so the fifth resource returns much less than the fourth — see §3</t>
+          <t>32.5 h/day → 28 working days. Beyond Sprint 1 the chain is sequential, so the fifth resource returns much less than the fourth — see §3</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6826,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Sprint 2 (30 September – 20 October) — 280 hours</t>
+          <t>Sprint 2 (30 September – 20 October) — 301 hours</t>
         </is>
       </c>
     </row>
@@ -7320,10 +7333,10 @@
         </is>
       </c>
       <c r="D65" s="8" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E65" s="8" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="66">
@@ -7335,10 +7348,10 @@
       <c r="B66" s="10" t="inlineStr"/>
       <c r="C66" s="9" t="inlineStr"/>
       <c r="D66" s="10" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>13.7</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="67">
@@ -7480,10 +7493,10 @@
       <c r="B73" s="10" t="inlineStr"/>
       <c r="C73" s="9" t="inlineStr"/>
       <c r="D73" s="10" t="n">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>43.1</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="75">

--- a/60-delivery/FlatWire_TrialRunPlan.xlsx
+++ b/60-delivery/FlatWire_TrialRunPlan.xlsx
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Shell layout and the 1280×1024 shopfloor canvas</t>
+          <t>Shell layout and the 1920×1080 shopfloor canvas</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">

--- a/60-delivery/FlatWire_TrialRunPlan.xlsx
+++ b/60-delivery/FlatWire_TrialRunPlan.xlsx
@@ -2247,7 +2247,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Shell layout and the 1280×1024 shopfloor canvas</t>
+          <t>Shell layout and the 1920×1080 shopfloor canvas</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>FlatWireRun(LineId, Status) index</t>
+          <t>FlatWireRun(MachineName, Status) index</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">

--- a/60-delivery/FlatWire_TrialRunPlan.xlsx
+++ b/60-delivery/FlatWire_TrialRunPlan.xlsx
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Fifteen thin controllers over UAController</t>
+          <t>Fourteen thin controllers over UAController</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
